--- a/data/trans_orig/P20D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25544</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44107</t>
+          <t>44686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>501</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>722</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>845</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26036</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
